--- a/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_ESG.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Bailey (21 L)</t>
+          <t>J. Bailey (40 L)</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Bailey (10.0 3PA)</t>
+          <t>J. Bailey (20.0 3PA)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P. Carvalhal (1.077)</t>
+          <t>D. Carr (1.154)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Above the Break 3 (25 L)</t>
+          <t>Above the Break 3 (42 L)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Restricted Area (58.8%)</t>
+          <t>Restricted Area (52.8%)</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -592,7 +592,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -944,223 +944,223 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>12</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
         <v>5</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>10</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>10.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>52.4%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>47.6%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0.6190476190476191</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
         <v>5</v>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>500.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>400.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -1196,53 +1196,53 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L3" t="n">
         <v>5</v>
       </c>
-      <c r="I3" t="n">
-        <v>14</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
         <v>4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.076923076923077</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -1292,16 +1292,26 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
@@ -1311,11 +1321,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1324,11 +1334,11 @@
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1337,7 +1347,7 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1349,18 +1359,18 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY3" t="n">
         <v>2</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
@@ -1368,31 +1378,31 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -1414,121 +1424,121 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>264552</t>
+          <t>191364</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>7</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -1539,37 +1549,37 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AN4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1581,18 +1591,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
         <v>5</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
@@ -1600,31 +1610,709 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
         <v>5</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ESG_D._CARR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>D. Carr</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ESG_Y._ANTONIO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>264552</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Y. Antonio</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>76.9%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>500.0%</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BG4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>4</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -1639,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1668,7 +2356,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -1686,7 +2374,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -2024,49 +2712,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>209936</t>
-        </is>
-      </c>
+          <t>ESG_D._CARR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>13</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -2075,16 +2759,16 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.076923076923077</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -2099,25 +2783,25 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -2125,7 +2809,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -2138,7 +2822,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -2157,25 +2841,25 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -2183,50 +2867,50 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AV2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="BA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
         </is>
       </c>
       <c r="BG2" t="n">
@@ -2256,181 +2940,191 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>264552</t>
+          <t>209936</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
         <v>5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>9</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="AH3" t="n">
         <v>7</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AN3" t="n">
+      <c r="AQ3" t="n">
         <v>7</v>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3</v>
-      </c>
       <c r="AR3" t="inlineStr">
         <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AV3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
         <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -2438,27 +3132,27 @@
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
         <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
@@ -2488,229 +3182,209 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>322878</t>
+          <t>264552</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
         <v>5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V4" t="n">
-        <v>9</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AE4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AK4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AQ4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
         <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
         <v>5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
@@ -2718,7 +3392,709 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>191364</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>322878</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>27</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>20</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>12</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>4</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -2733,7 +4109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2762,7 +4138,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -2780,7 +4156,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -3132,223 +4508,223 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>12</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
         <v>5</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>10</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>10.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>52.4%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>47.6%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0.6190476190476191</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
         <v>5</v>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>500.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>400.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -3384,53 +4760,53 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L3" t="n">
         <v>5</v>
       </c>
-      <c r="I3" t="n">
-        <v>14</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
         <v>4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.076923076923077</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -3441,11 +4817,11 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -3454,11 +4830,11 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3467,7 +4843,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -3480,16 +4856,26 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
@@ -3499,11 +4885,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -3512,11 +4898,11 @@
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -3525,7 +4911,7 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -3537,18 +4923,18 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY3" t="n">
         <v>2</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
@@ -3556,31 +4942,31 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -3602,87 +4988,83 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>264552</t>
-        </is>
-      </c>
+          <t>ESG_D._CARR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -3690,33 +5072,33 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -3727,20 +5109,20 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AQ4" t="n">
@@ -3748,71 +5130,753 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>191364</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ESG_Y._ANTONIO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>264552</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Y. Antonio</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>76.9%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>8</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AV4" t="n">
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
         <v>3</v>
       </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY4" t="n">
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
         <v>5</v>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BD7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
         <v>3</v>
       </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>500.0%</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BG4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -3827,15 +5891,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -4212,67 +6276,67 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>322878</t>
+          <t>209936</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -4287,7 +6351,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -4296,24 +6360,24 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -4326,7 +6390,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -4335,26 +6399,16 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
@@ -4365,7 +6419,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -4374,75 +6428,327 @@
         </is>
       </c>
       <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>322878</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>27</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
         <v>5</v>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
         <v>5</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>500.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>400.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -4468,7 +6774,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -4612,21 +6918,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.84</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4635,14 +6941,14 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4653,7 +6959,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4669,7 +6975,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -4695,27 +7001,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.176470588235294</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -4725,7 +7031,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -4778,27 +7084,27 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
         <v>12</v>
       </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -4808,7 +7114,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -4819,7 +7125,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -4827,7 +7133,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -4835,7 +7141,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -4861,27 +7167,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -4891,18 +7197,18 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -4910,11 +7216,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>500.0%</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4934,25 +7246,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -4961,18 +7273,18 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -4990,8 +7302,14 @@
           <t>500.0%</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5011,11 +7329,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -5025,11 +7343,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -5038,14 +7356,14 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -5056,7 +7374,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -5064,7 +7382,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -5081,7 +7399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5092,7 +7410,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -5236,27 +7554,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.176470588235294</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="J2" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -5266,7 +7584,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -5315,48 +7633,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.84</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>25</v>
-      </c>
-      <c r="M3" t="n">
-        <v>7</v>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -5364,15 +7682,15 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -5398,68 +7716,234 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>26.2%</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>42</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>32.1%</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>8.4%</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -5469,6 +7953,1046 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="29" customWidth="1" min="22" max="22"/>
+    <col width="38" customWidth="1" min="23" max="23"/>
+    <col width="35" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>team_key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>global_player_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fg2a</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg2m</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>eligible_zone_profile</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume_all</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct_all</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume_qualified</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct_qualified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322878</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>209936</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322878</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ESG_Y._ANTONIO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>264552</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Y. Antonio</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>322878</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>209936</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>26.9%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ESG_D._CARR</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>D. Carr</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>191364</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>322878</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5658,68 +9182,68 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.3333333333333333</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +9284,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
         <v>5</v>
@@ -5770,14 +9294,14 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.428571428571429</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
         <v>5</v>
@@ -5790,7 +9314,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -5858,7 +9382,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -5868,11 +9392,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -5881,14 +9405,14 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P4" t="n">
         <v>4</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -5907,7 +9431,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -5952,31 +9476,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -5986,7 +9510,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -5997,7 +9521,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -6005,7 +9529,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -6013,7 +9537,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -6050,328 +9574,68 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:X2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="25" customWidth="1" min="20" max="20"/>
-    <col width="32" customWidth="1" min="21" max="21"/>
-    <col width="29" customWidth="1" min="22" max="22"/>
-    <col width="38" customWidth="1" min="23" max="23"/>
-    <col width="35" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>team_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>team_code</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>team_key</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>player_id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>global_player_id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>player_name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>zone</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>attempts</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>made</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>fg_pct</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>pps</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>fg2a</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>fg2m</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>fg3a</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>fg3m</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>zone_share</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>eligible_zone_profile</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_volume</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_pct</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_volume_all</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_pct_all</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_volume_qualified</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_pct_qualified</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Esgueira Aveiro OLI</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ESG</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ESG</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ESG_J._BAILEY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>322878</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>J. Bailey</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
